--- a/artfynd/A 2837-2025 artfynd.xlsx
+++ b/artfynd/A 2837-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>17147546</v>
       </c>
       <c r="B2" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592214.0648524038</v>
+        <v>592214</v>
       </c>
       <c r="R2" t="n">
-        <v>6508942.079296299</v>
+        <v>6508942</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,19 +753,9 @@
           <t>2014-12-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-12-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -806,12 +791,7 @@
         <v>17147547</v>
       </c>
       <c r="B3" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -853,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592180.2260384323</v>
+        <v>592180</v>
       </c>
       <c r="R3" t="n">
-        <v>6509007.794380617</v>
+        <v>6509008</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,19 +866,9 @@
           <t>2014-12-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-12-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -941,15 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17147557</v>
+        <v>17147549</v>
       </c>
       <c r="B4" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,7 +941,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -991,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592136.1834348988</v>
+        <v>592171</v>
       </c>
       <c r="R4" t="n">
-        <v>6508998.953993917</v>
+        <v>6509005</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,27 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-12-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-12-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-12-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2014-12-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1079,15 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17147549</v>
+        <v>17147557</v>
       </c>
       <c r="B5" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1059,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1129,13 +1074,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592170.9218665123</v>
+        <v>592136</v>
       </c>
       <c r="R5" t="n">
-        <v>6509004.975154901</v>
+        <v>6508999</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1159,22 +1104,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-12-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-12-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-12-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-12-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2837-2025 artfynd.xlsx
+++ b/artfynd/A 2837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17147546</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17147547</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17147549</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,8 +1169,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17147557</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>